--- a/Data Files/EDEN/Holiday_List.xlsx
+++ b/Data Files/EDEN/Holiday_List.xlsx
@@ -28,7 +28,7 @@
     <t>Manjunath Batti</t>
   </si>
   <si>
-    <t>Privilege Leave</t>
+    <t>Privilege/Annual Leave</t>
   </si>
 </sst>
 </file>
